--- a/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141838</t>
+    <t>20260220142104</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:38+01:00</t>
+    <t>2026-02-20T14:21:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>Evaluation CIM11</t>
+  </si>
+  <si>
+    <t>GEN-092.04.24</t>
+  </si>
+  <si>
+    <t>Autre type d'évaluation</t>
   </si>
   <si>
     <t/>
@@ -423,7 +429,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -515,15 +521,23 @@
         <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142104</t>
+    <t>20260311144903</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:04+01:00</t>
+    <t>2026-03-11T14:49:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150250</t>
+    <t>20260619134042</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:50+01:00</t>
+    <t>2026-06-19T13:40:42+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134042</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:42+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-type-evaluation-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134042</t>
+    <t>20260716085852</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:42+01:00</t>
+    <t>2026-07-16T08:58:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
